--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
@@ -1153,7 +1153,7 @@
     <t>['26', '40']</t>
   </si>
   <si>
-    <t>['39', '52', '103']</t>
+    <t>['103', '39', '52']</t>
   </si>
   <si>
     <t>['42', '45+3']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
@@ -25581,10 +25581,10 @@
         <v>5</v>
       </c>
       <c r="BB115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD115" t="n">
         <v>1.72</v>
@@ -26889,10 +26889,10 @@
         <v>6</v>
       </c>
       <c r="BB121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD121" t="n">
         <v>1.29</v>
@@ -32993,10 +32993,10 @@
         <v>2</v>
       </c>
       <c r="BB149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD149" t="n">
         <v>1.85</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
@@ -101854,10 +101854,10 @@
         <v>1.29</v>
       </c>
       <c r="AS465" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT465" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AU465" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
@@ -101552,73 +101552,73 @@
         </is>
       </c>
       <c r="Q464" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R464" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S464" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T464" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U464" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V464" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="W464" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X464" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y464" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z464" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA464" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AB464" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AC464" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD464" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE464" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF464" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AG464" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AH464" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI464" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ464" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK464" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL464" t="n">
         <v>0</v>
       </c>
       <c r="AM464" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN464" t="n">
         <v>1.79</v>
@@ -101669,43 +101669,43 @@
         <v>5</v>
       </c>
       <c r="BD464" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BE464" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF464" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG464" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BH464" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BI464" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BJ464" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BK464" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BL464" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BM464" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BN464" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BO464" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP464" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="465">
@@ -101770,73 +101770,73 @@
         </is>
       </c>
       <c r="Q465" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R465" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S465" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="T465" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U465" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V465" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W465" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X465" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y465" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z465" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA465" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB465" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AC465" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD465" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE465" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF465" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AG465" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH465" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI465" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AJ465" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK465" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL465" t="n">
         <v>0</v>
       </c>
       <c r="AM465" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AN465" t="n">
         <v>1.74</v>
@@ -101887,43 +101887,43 @@
         <v>10</v>
       </c>
       <c r="BD465" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BE465" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF465" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BG465" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BH465" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BI465" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BJ465" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BK465" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BL465" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BM465" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BN465" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BO465" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP465" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Spain Segunda División_20242025.xlsx
@@ -96849,19 +96849,19 @@
         <v>3</v>
       </c>
       <c r="AV442" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW442" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX442" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY442" t="n">
         <v>7</v>
       </c>
-      <c r="AY442" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ442" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA442" t="n">
         <v>9</v>
@@ -97064,22 +97064,22 @@
         <v>2.52</v>
       </c>
       <c r="AU443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY443" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ443" t="n">
         <v>3</v>
-      </c>
-      <c r="AV443" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW443" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX443" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY443" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ443" t="n">
-        <v>5</v>
       </c>
       <c r="BA443" t="n">
         <v>0</v>
@@ -97282,22 +97282,22 @@
         <v>2.8</v>
       </c>
       <c r="AU444" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV444" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW444" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX444" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY444" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ444" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BA444" t="n">
         <v>4</v>
@@ -97506,16 +97506,16 @@
         <v>1</v>
       </c>
       <c r="AW445" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AX445" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY445" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ445" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA445" t="n">
         <v>3</v>
@@ -97718,22 +97718,22 @@
         <v>2.83</v>
       </c>
       <c r="AU446" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV446" t="n">
         <v>2</v>
       </c>
       <c r="AW446" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AX446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY446" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ446" t="n">
         <v>3</v>
-      </c>
-      <c r="AY446" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ446" t="n">
-        <v>5</v>
       </c>
       <c r="BA446" t="n">
         <v>11</v>
@@ -98160,16 +98160,16 @@
         <v>7</v>
       </c>
       <c r="AW448" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX448" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY448" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ448" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA448" t="n">
         <v>4</v>
@@ -98372,22 +98372,22 @@
         <v>2.82</v>
       </c>
       <c r="AU449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV449" t="n">
         <v>1</v>
       </c>
       <c r="AW449" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX449" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AY449" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ449" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA449" t="n">
         <v>4</v>
@@ -98590,22 +98590,22 @@
         <v>2.74</v>
       </c>
       <c r="AU450" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV450" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW450" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX450" t="n">
         <v>3</v>
       </c>
-      <c r="AV450" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW450" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX450" t="n">
+      <c r="AY450" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ450" t="n">
         <v>5</v>
-      </c>
-      <c r="AY450" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ450" t="n">
-        <v>7</v>
       </c>
       <c r="BA450" t="n">
         <v>9</v>
@@ -98808,19 +98808,19 @@
         <v>2.79</v>
       </c>
       <c r="AU451" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV451" t="n">
         <v>9</v>
       </c>
       <c r="AW451" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX451" t="n">
         <v>5</v>
       </c>
       <c r="AY451" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ451" t="n">
         <v>14</v>
@@ -99029,19 +99029,19 @@
         <v>9</v>
       </c>
       <c r="AV452" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW452" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AX452" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY452" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ452" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA452" t="n">
         <v>8</v>
@@ -101633,13 +101633,13 @@
         <v>1.77</v>
       </c>
       <c r="AR464" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AS464" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AT464" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AU464" t="n">
         <v>4</v>
@@ -101854,10 +101854,10 @@
         <v>1.29</v>
       </c>
       <c r="AS465" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AT465" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AU465" t="n">
         <v>5</v>
